--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -31,13 +31,13 @@
     <t>Purgatory</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
-  </si>
-  <si>
     <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Coaster</t>
+  </si>
+  <si>
+    <t>Purgatory Passes</t>
   </si>
   <si>
     <t>Purgatory Comp Tickets</t>
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C2" s="2">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C3" s="2">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -465,10 +465,10 @@
         <v>45633</v>
       </c>
       <c r="C4" s="2">
-        <v>60</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45633</v>
+        <v>45628</v>
       </c>
       <c r="C5" s="2">
-        <v>295</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="C6" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="C7" s="2">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="C8" s="2">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C9" s="2">
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +560,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C11" s="2">
-        <v>580</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +574,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C12" s="2">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,13 +588,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C13" s="2">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -605,10 +605,10 @@
         <v>45633</v>
       </c>
       <c r="C14" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>168</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,10 +644,10 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C18" s="2">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C19" s="2">
-        <v>337</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +686,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45629</v>
+        <v>45631</v>
       </c>
       <c r="C20" s="2">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
@@ -700,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C22" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C23" s="2">
-        <v>417</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C24" s="2">
-        <v>114</v>
+        <v>-3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C25" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C26" s="2">
-        <v>2</v>
+        <v>117</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45634</v>
+        <v>45631</v>
       </c>
       <c r="C27" s="2">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C28" s="2">
-        <v>1260</v>
+        <v>27</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45628</v>
+        <v>45633</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45628</v>
+        <v>45633</v>
       </c>
       <c r="C30" s="2">
-        <v>85</v>
+        <v>1558</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +840,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45628</v>
+        <v>45634</v>
       </c>
       <c r="C31" s="2">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -854,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C33" s="2">
-        <v>89</v>
+        <v>337</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45634</v>
+        <v>45629</v>
       </c>
       <c r="C34" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45629</v>
+        <v>45631</v>
       </c>
       <c r="C37" s="2">
-        <v>-3</v>
+        <v>417</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>7</v>
@@ -938,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C38" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45630</v>
+        <v>45632</v>
       </c>
       <c r="C39" s="2">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45631</v>
+        <v>45633</v>
       </c>
       <c r="C40" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +980,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C41" s="2">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>8</v>
@@ -994,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C42" s="2">
-        <v>149</v>
+        <v>1260</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45633</v>
+        <v>45629</v>
       </c>
       <c r="C43" s="2">
-        <v>1558</v>
+        <v>85</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C44" s="2">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C45" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45628</v>
+        <v>45633</v>
       </c>
       <c r="C46" s="2">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45629</v>
+        <v>45634</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C48" s="2">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1092,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C49" s="2">
-        <v>392</v>
+        <v>160</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45630</v>
+        <v>45628</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45631</v>
+        <v>45629</v>
       </c>
       <c r="C52" s="2">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45633</v>
+        <v>45631</v>
       </c>
       <c r="C54" s="2">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C55" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C56" s="2">
-        <v>168</v>
+        <v>580</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C3" s="2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C4" s="2">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -479,10 +479,10 @@
         <v>45633</v>
       </c>
       <c r="C5" s="2">
-        <v>295</v>
+        <v>3</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45629</v>
+        <v>45633</v>
       </c>
       <c r="C6" s="2">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C7" s="2">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>5</v>
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +560,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +574,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C12" s="2">
-        <v>160</v>
+        <v>295</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -591,10 +591,10 @@
         <v>45628</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="C14" s="2">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="C15" s="2">
-        <v>8</v>
+        <v>368</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -633,10 +633,10 @@
         <v>45631</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="C17" s="2">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>580</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,10 +672,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45634</v>
+        <v>45628</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>5</v>
@@ -689,10 +689,10 @@
         <v>45628</v>
       </c>
       <c r="C20" s="2">
-        <v>337</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,10 +700,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45629</v>
+        <v>45628</v>
       </c>
       <c r="C21" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -714,10 +714,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45630</v>
+        <v>45631</v>
       </c>
       <c r="C22" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -731,10 +731,10 @@
         <v>45631</v>
       </c>
       <c r="C23" s="2">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +742,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C24" s="2">
-        <v>417</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -756,10 +756,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C25" s="2">
-        <v>114</v>
+        <v>2</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C26" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45633</v>
+        <v>45629</v>
       </c>
       <c r="C27" s="2">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,10 +798,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45634</v>
+        <v>45629</v>
       </c>
       <c r="C28" s="2">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>8</v>
@@ -812,10 +812,10 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45634</v>
+        <v>45630</v>
       </c>
       <c r="C29" s="2">
-        <v>1260</v>
+        <v>117</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -826,10 +826,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C30" s="2">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -840,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C32" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C33" s="2">
-        <v>392</v>
+        <v>1558</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C34" s="2">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,10 +896,10 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C35" s="2">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -910,10 +910,10 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45631</v>
+        <v>45628</v>
       </c>
       <c r="C36" s="2">
-        <v>86</v>
+        <v>337</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -924,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45633</v>
+        <v>45630</v>
       </c>
       <c r="C38" s="2">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45633</v>
+        <v>45631</v>
       </c>
       <c r="C39" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,10 +966,10 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45634</v>
+        <v>45631</v>
       </c>
       <c r="C40" s="2">
-        <v>168</v>
+        <v>417</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -980,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45628</v>
+        <v>45632</v>
       </c>
       <c r="C41" s="2">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +994,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="C42" s="2">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1008,10 +1008,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45629</v>
+        <v>45633</v>
       </c>
       <c r="C43" s="2">
-        <v>368</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1022,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C44" s="2">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,10 +1036,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45632</v>
+        <v>45634</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>1260</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,10 +1050,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C46" s="2">
-        <v>580</v>
+        <v>88</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,7 +1064,7 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -1078,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="C48" s="2">
-        <v>-3</v>
+        <v>20</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1092,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45629</v>
+        <v>45630</v>
       </c>
       <c r="C49" s="2">
-        <v>21</v>
+        <v>392</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1109,7 +1109,7 @@
         <v>45630</v>
       </c>
       <c r="C50" s="2">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1120,10 +1120,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C51" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1134,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45632</v>
+        <v>45631</v>
       </c>
       <c r="C52" s="2">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,10 +1148,10 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45633</v>
+        <v>45632</v>
       </c>
       <c r="C53" s="2">
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1165,10 +1165,10 @@
         <v>45633</v>
       </c>
       <c r="C54" s="2">
-        <v>1558</v>
+        <v>62</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45634</v>
+        <v>45633</v>
       </c>
       <c r="C55" s="2">
-        <v>160</v>
+        <v>11</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>45634</v>
       </c>
       <c r="C56" s="2">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -31,19 +31,19 @@
     <t>Purgatory</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Passes</t>
   </si>
   <si>
     <t>Purgatory Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Uplift Tickets</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
 </sst>
 </file>
@@ -406,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C2" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45629</v>
+        <v>45635</v>
       </c>
       <c r="C3" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,10 +462,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45632</v>
+        <v>45635</v>
       </c>
       <c r="C4" s="2">
-        <v>113</v>
+        <v>360</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -476,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45633</v>
+        <v>45635</v>
       </c>
       <c r="C5" s="2">
-        <v>3</v>
+        <v>135</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45633</v>
+        <v>45635</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45634</v>
+        <v>45635</v>
       </c>
       <c r="C9" s="2">
-        <v>160</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,10 +546,10 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45630</v>
+        <v>45636</v>
       </c>
       <c r="C10" s="2">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>6</v>
@@ -560,13 +560,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="C11" s="2">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,10 +574,10 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="C12" s="2">
-        <v>295</v>
+        <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -588,13 +588,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45628</v>
+        <v>45636</v>
       </c>
       <c r="C13" s="2">
-        <v>15</v>
+        <v>397</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45629</v>
+        <v>45636</v>
       </c>
       <c r="C14" s="2">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45629</v>
+        <v>45636</v>
       </c>
       <c r="C15" s="2">
-        <v>368</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45631</v>
+        <v>45636</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45632</v>
+        <v>45637</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45632</v>
+        <v>45637</v>
       </c>
       <c r="C18" s="2">
-        <v>580</v>
+        <v>36</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45628</v>
+        <v>45637</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +686,10 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45628</v>
+        <v>45637</v>
       </c>
       <c r="C20" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>6</v>
@@ -700,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45628</v>
+        <v>45637</v>
       </c>
       <c r="C21" s="2">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45631</v>
+        <v>45637</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45631</v>
+        <v>45637</v>
       </c>
       <c r="C23" s="2">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>6</v>
@@ -742,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45628</v>
+        <v>45638</v>
       </c>
       <c r="C26" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45629</v>
+        <v>45638</v>
       </c>
       <c r="C27" s="2">
-        <v>-3</v>
+        <v>102</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45629</v>
+        <v>45638</v>
       </c>
       <c r="C28" s="2">
-        <v>21</v>
+        <v>457</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45630</v>
+        <v>45638</v>
       </c>
       <c r="C29" s="2">
-        <v>117</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45631</v>
+        <v>45638</v>
       </c>
       <c r="C30" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45632</v>
+        <v>45638</v>
       </c>
       <c r="C31" s="2">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="C32" s="2">
-        <v>149</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="C33" s="2">
-        <v>1558</v>
+        <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C34" s="2">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>6</v>
@@ -896,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45634</v>
+        <v>45639</v>
       </c>
       <c r="C35" s="2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45628</v>
+        <v>45639</v>
       </c>
       <c r="C36" s="2">
-        <v>337</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45629</v>
+        <v>45639</v>
       </c>
       <c r="C37" s="2">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45630</v>
+        <v>45639</v>
       </c>
       <c r="C38" s="2">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45631</v>
+        <v>45639</v>
       </c>
       <c r="C39" s="2">
-        <v>16</v>
+        <v>573</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45631</v>
+        <v>45639</v>
       </c>
       <c r="C40" s="2">
-        <v>417</v>
+        <v>265</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45632</v>
+        <v>45639</v>
       </c>
       <c r="C41" s="2">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45632</v>
+        <v>45639</v>
       </c>
       <c r="C42" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45633</v>
+        <v>45639</v>
       </c>
       <c r="C43" s="2">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45634</v>
+        <v>45640</v>
       </c>
       <c r="C44" s="2">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45634</v>
+        <v>45640</v>
       </c>
       <c r="C45" s="2">
-        <v>1260</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45628</v>
+        <v>45640</v>
       </c>
       <c r="C46" s="2">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45629</v>
+        <v>45640</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C48" s="2">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C49" s="2">
-        <v>392</v>
+        <v>129</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45630</v>
+        <v>45640</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>1413</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45631</v>
+        <v>45640</v>
       </c>
       <c r="C52" s="2">
-        <v>86</v>
+        <v>570</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45632</v>
+        <v>45640</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="C54" s="2">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="C55" s="2">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,195 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45634</v>
+        <v>45641</v>
       </c>
       <c r="C56" s="2">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C58" s="2">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C59" s="2">
+        <v>2</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C60" s="2">
+        <v>99</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C61" s="2">
+        <v>100</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C62" s="2">
+        <v>137</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1125</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C64" s="2">
+        <v>403</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C66" s="2">
+        <v>6</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C67" s="2">
+        <v>6</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C69" s="2">
+        <v>88</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
-    <t>Purgatory Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Coaster</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -437,7 +434,7 @@
         <v>45635</v>
       </c>
       <c r="C2" s="2">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -451,10 +448,10 @@
         <v>45635</v>
       </c>
       <c r="C3" s="2">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -465,7 +462,7 @@
         <v>45635</v>
       </c>
       <c r="C4" s="2">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -479,10 +476,10 @@
         <v>45635</v>
       </c>
       <c r="C5" s="2">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -493,10 +490,10 @@
         <v>45635</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>504</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -507,10 +504,10 @@
         <v>45635</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>735</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -521,10 +518,10 @@
         <v>45635</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +529,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C9" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -552,7 +549,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -563,7 +560,7 @@
         <v>45636</v>
       </c>
       <c r="C11" s="2">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -577,7 +574,7 @@
         <v>45636</v>
       </c>
       <c r="C12" s="2">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>6</v>
@@ -591,10 +588,10 @@
         <v>45636</v>
       </c>
       <c r="C13" s="2">
-        <v>397</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -605,10 +602,10 @@
         <v>45636</v>
       </c>
       <c r="C14" s="2">
-        <v>135</v>
+        <v>338</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -619,10 +616,10 @@
         <v>45636</v>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>642</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -633,10 +630,10 @@
         <v>45636</v>
       </c>
       <c r="C16" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -650,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,7 +658,7 @@
         <v>45637</v>
       </c>
       <c r="C18" s="2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -675,7 +672,7 @@
         <v>45637</v>
       </c>
       <c r="C19" s="2">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
@@ -689,10 +686,10 @@
         <v>45637</v>
       </c>
       <c r="C20" s="2">
-        <v>514</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -703,10 +700,10 @@
         <v>45637</v>
       </c>
       <c r="C21" s="2">
-        <v>151</v>
+        <v>535</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -717,10 +714,10 @@
         <v>45637</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>778</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -731,10 +728,10 @@
         <v>45637</v>
       </c>
       <c r="C23" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -748,7 +745,7 @@
         <v>2</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -759,7 +756,7 @@
         <v>45638</v>
       </c>
       <c r="C25" s="2">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>6</v>
@@ -773,7 +770,7 @@
         <v>45638</v>
       </c>
       <c r="C26" s="2">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -787,10 +784,10 @@
         <v>45638</v>
       </c>
       <c r="C27" s="2">
-        <v>102</v>
+        <v>514</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -801,10 +798,10 @@
         <v>45638</v>
       </c>
       <c r="C28" s="2">
-        <v>457</v>
+        <v>714</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -815,10 +812,10 @@
         <v>45638</v>
       </c>
       <c r="C29" s="2">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C31" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +851,10 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C32" s="2">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -868,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C33" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C34" s="2">
-        <v>16</v>
+        <v>816</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -899,10 +896,10 @@
         <v>45639</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>807</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -913,10 +910,10 @@
         <v>45639</v>
       </c>
       <c r="C36" s="2">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C37" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -938,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C38" s="2">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C39" s="2">
-        <v>573</v>
+        <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C40" s="2">
-        <v>265</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,10 +1005,10 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C43" s="2">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>6</v>
@@ -1025,10 +1022,10 @@
         <v>45640</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1039,10 +1036,10 @@
         <v>45640</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>829</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1053,10 +1050,10 @@
         <v>45640</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>1649</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1067,10 +1064,10 @@
         <v>45640</v>
       </c>
       <c r="C47" s="2">
-        <v>5</v>
+        <v>166</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C48" s="2">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,10 +1089,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C49" s="2">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1106,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C50" s="2">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C51" s="2">
-        <v>1413</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C52" s="2">
-        <v>570</v>
+        <v>155</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C53" s="2">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C54" s="2">
-        <v>5</v>
+        <v>802</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C55" s="2">
-        <v>48</v>
+        <v>1165</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,192 +1190,10 @@
         <v>45641</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C57" s="2">
-        <v>1</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C58" s="2">
-        <v>2</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C59" s="2">
-        <v>2</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C60" s="2">
-        <v>99</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C61" s="2">
-        <v>100</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C62" s="2">
-        <v>137</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1125</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C64" s="2">
-        <v>403</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C65" s="2">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C66" s="2">
-        <v>6</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C67" s="2">
-        <v>6</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C68" s="2">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C69" s="2">
-        <v>88</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,22 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl</t>
+    <t>Purgatory</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Purgatory Coaster</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -403,13 +406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,7 +437,7 @@
         <v>45635</v>
       </c>
       <c r="C2" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,13 +448,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C3" s="2">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -459,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C4" s="2">
-        <v>65</v>
+        <v>514</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,10 +476,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C5" s="2">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C6" s="2">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -501,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C7" s="2">
-        <v>735</v>
+        <v>265</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C8" s="2">
-        <v>2</v>
+        <v>1413</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +535,10 @@
         <v>45636</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,7 +549,7 @@
         <v>45636</v>
       </c>
       <c r="C10" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>5</v>
@@ -557,10 +560,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C11" s="2">
-        <v>6</v>
+        <v>133</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>5</v>
@@ -571,13 +574,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C12" s="2">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,10 +588,10 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45636</v>
+        <v>45640</v>
       </c>
       <c r="C13" s="2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -599,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45636</v>
+        <v>45640</v>
       </c>
       <c r="C14" s="2">
-        <v>338</v>
+        <v>88</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C15" s="2">
-        <v>642</v>
+        <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,10 +633,10 @@
         <v>45636</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -655,7 +658,7 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
@@ -669,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C19" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +686,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C20" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,10 +700,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C21" s="2">
-        <v>535</v>
+        <v>145</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>5</v>
@@ -711,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C22" s="2">
-        <v>778</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C23" s="2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,10 +742,10 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C24" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -753,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C25" s="2">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C26" s="2">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -781,10 +784,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C27" s="2">
-        <v>514</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -795,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45638</v>
+        <v>45636</v>
       </c>
       <c r="C28" s="2">
-        <v>714</v>
+        <v>3</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -809,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45638</v>
+        <v>45637</v>
       </c>
       <c r="C29" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,10 +826,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
@@ -837,10 +840,10 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C31" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
@@ -851,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C32" s="2">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -865,10 +868,10 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45639</v>
+        <v>45641</v>
       </c>
       <c r="C33" s="2">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
@@ -879,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="C34" s="2">
-        <v>816</v>
+        <v>360</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -893,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="C35" s="2">
-        <v>807</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C36" s="2">
-        <v>49</v>
+        <v>457</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>193</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,10 +938,10 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C38" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
@@ -966,7 +969,7 @@
         <v>45640</v>
       </c>
       <c r="C40" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -977,10 +980,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C41" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -991,13 +994,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>403</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,13 +1008,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C43" s="2">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C44" s="2">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1033,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C45" s="2">
-        <v>829</v>
+        <v>25</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1047,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C46" s="2">
-        <v>1649</v>
+        <v>98</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45640</v>
+        <v>45637</v>
       </c>
       <c r="C47" s="2">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,10 +1078,10 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C48" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1089,10 +1092,10 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C49" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1103,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C50" s="2">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,10 +1120,10 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45641</v>
+        <v>45639</v>
       </c>
       <c r="C51" s="2">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1131,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C52" s="2">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,7 +1151,7 @@
         <v>45641</v>
       </c>
       <c r="C53" s="2">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
@@ -1162,10 +1165,10 @@
         <v>45641</v>
       </c>
       <c r="C54" s="2">
-        <v>802</v>
+        <v>99</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,7 +1179,7 @@
         <v>45641</v>
       </c>
       <c r="C55" s="2">
-        <v>1165</v>
+        <v>100</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>7</v>
@@ -1187,13 +1190,195 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
+        <v>45636</v>
+      </c>
+      <c r="C56" s="2">
+        <v>397</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45637</v>
+      </c>
+      <c r="C57" s="2">
+        <v>151</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45637</v>
+      </c>
+      <c r="C58" s="2">
+        <v>4</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45638</v>
+      </c>
+      <c r="C59" s="2">
+        <v>2</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45639</v>
+      </c>
+      <c r="C60" s="2">
+        <v>573</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C61" s="2">
+        <v>570</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C62" s="2">
+        <v>48</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="2">
         <v>45641</v>
       </c>
-      <c r="C56" s="2">
-        <v>98</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
+      <c r="C63" s="2">
+        <v>6</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C64" s="2">
+        <v>135</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45639</v>
+      </c>
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45639</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45639</v>
+      </c>
+      <c r="C67" s="2">
+        <v>32</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45641</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1125</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -31,16 +31,16 @@
     <t>Purgatory</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Coaster</t>
+    <t>Purgatory Tickets</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
@@ -434,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C2" s="2">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -451,7 +451,7 @@
         <v>45636</v>
       </c>
       <c r="C3" s="2">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -465,10 +465,10 @@
         <v>45637</v>
       </c>
       <c r="C4" s="2">
-        <v>514</v>
+        <v>133</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C7" s="2">
-        <v>265</v>
+        <v>88</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C8" s="2">
-        <v>1413</v>
+        <v>135</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C9" s="2">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C10" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +560,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C11" s="2">
-        <v>133</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +574,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,13 +588,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C13" s="2">
-        <v>1</v>
+        <v>1125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C14" s="2">
-        <v>88</v>
+        <v>397</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C15" s="2">
-        <v>1</v>
+        <v>151</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -647,10 +647,10 @@
         <v>45638</v>
       </c>
       <c r="C17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +658,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>573</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>570</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +686,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C20" s="2">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C21" s="2">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C22" s="2">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C24" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +756,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C25" s="2">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
@@ -770,13 +770,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C26" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C27" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,10 +798,10 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45636</v>
+        <v>45640</v>
       </c>
       <c r="C28" s="2">
-        <v>3</v>
+        <v>129</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -812,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C29" s="2">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C30" s="2">
-        <v>102</v>
+        <v>360</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C31" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C32" s="2">
-        <v>129</v>
+        <v>457</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C33" s="2">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C34" s="2">
-        <v>360</v>
+        <v>16</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C35" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C36" s="2">
-        <v>457</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +924,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C37" s="2">
-        <v>193</v>
+        <v>1</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>6</v>
@@ -938,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C38" s="2">
-        <v>16</v>
+        <v>403</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +952,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C40" s="2">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,10 +994,10 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C42" s="2">
-        <v>403</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>6</v>
@@ -1008,13 +1008,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1022,13 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C44" s="2">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1036,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C45" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1050,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C46" s="2">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C48" s="2">
         <v>2</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1092,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C49" s="2">
         <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C50" s="2">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45639</v>
+        <v>45641</v>
       </c>
       <c r="C51" s="2">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1134,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C52" s="2">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C54" s="2">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1176,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C55" s="2">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,13 +1190,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45636</v>
+        <v>45638</v>
       </c>
       <c r="C56" s="2">
-        <v>397</v>
+        <v>2</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1204,13 +1204,13 @@
         <v>4</v>
       </c>
       <c r="B57" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C57" s="2">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1218,13 +1218,13 @@
         <v>4</v>
       </c>
       <c r="B58" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C58" s="2">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1232,13 +1232,13 @@
         <v>4</v>
       </c>
       <c r="B59" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C59" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1246,13 +1246,13 @@
         <v>4</v>
       </c>
       <c r="B60" s="2">
-        <v>45639</v>
+        <v>45641</v>
       </c>
       <c r="C60" s="2">
-        <v>573</v>
+        <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1260,13 +1260,13 @@
         <v>4</v>
       </c>
       <c r="B61" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C61" s="2">
-        <v>570</v>
+        <v>99</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>4</v>
       </c>
       <c r="B62" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C62" s="2">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>5</v>
@@ -1288,13 +1288,13 @@
         <v>4</v>
       </c>
       <c r="B63" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C63" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1302,13 +1302,13 @@
         <v>4</v>
       </c>
       <c r="B64" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C64" s="2">
         <v>135</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1316,13 +1316,13 @@
         <v>4</v>
       </c>
       <c r="B65" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C65" s="2">
-        <v>1</v>
+        <v>514</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1330,13 +1330,13 @@
         <v>4</v>
       </c>
       <c r="B66" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C66" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1344,13 +1344,13 @@
         <v>4</v>
       </c>
       <c r="B67" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C67" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1358,13 +1358,13 @@
         <v>4</v>
       </c>
       <c r="B68" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C68" s="2">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1372,13 +1372,13 @@
         <v>4</v>
       </c>
       <c r="B69" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C69" s="2">
-        <v>1125</v>
+        <v>1413</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -437,7 +434,7 @@
         <v>45636</v>
       </c>
       <c r="C2" s="2">
-        <v>51</v>
+        <v>642</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C3" s="2">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C4" s="2">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -479,10 +476,10 @@
         <v>45639</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>807</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -493,7 +490,7 @@
         <v>45640</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -504,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C7" s="2">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -521,10 +518,10 @@
         <v>45635</v>
       </c>
       <c r="C8" s="2">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +529,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C9" s="2">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -549,10 +546,10 @@
         <v>45639</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C11" s="2">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C12" s="2">
-        <v>1</v>
+        <v>1165</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C13" s="2">
-        <v>1125</v>
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -605,10 +602,10 @@
         <v>45636</v>
       </c>
       <c r="C14" s="2">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C15" s="2">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C16" s="2">
-        <v>4</v>
+        <v>816</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C18" s="2">
-        <v>573</v>
+        <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C19" s="2">
-        <v>570</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C20" s="2">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C21" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C22" s="2">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C23" s="2">
         <v>2</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C24" s="2">
-        <v>3</v>
+        <v>535</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +753,13 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C25" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +767,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C26" s="2">
-        <v>102</v>
+        <v>829</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C28" s="2">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C29" s="2">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C30" s="2">
-        <v>360</v>
+        <v>6</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C31" s="2">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -857,10 +854,10 @@
         <v>45638</v>
       </c>
       <c r="C32" s="2">
-        <v>457</v>
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C33" s="2">
-        <v>193</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C34" s="2">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +893,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C36" s="2">
-        <v>7</v>
+        <v>735</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,10 +921,10 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>6</v>
@@ -938,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C38" s="2">
-        <v>403</v>
+        <v>714</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,10 +949,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45641</v>
+        <v>45639</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>6</v>
@@ -969,10 +966,10 @@
         <v>45641</v>
       </c>
       <c r="C40" s="2">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -983,10 +980,10 @@
         <v>45635</v>
       </c>
       <c r="C41" s="2">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -997,10 +994,10 @@
         <v>45636</v>
       </c>
       <c r="C42" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45638</v>
+        <v>45637</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1025,10 +1022,10 @@
         <v>45638</v>
       </c>
       <c r="C44" s="2">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C45" s="2">
-        <v>1</v>
+        <v>514</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,13 +1047,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C46" s="2">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1067,10 +1064,10 @@
         <v>45640</v>
       </c>
       <c r="C47" s="2">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1081,10 +1078,10 @@
         <v>45641</v>
       </c>
       <c r="C48" s="2">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1095,10 +1092,10 @@
         <v>45641</v>
       </c>
       <c r="C49" s="2">
-        <v>2</v>
+        <v>802</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C50" s="2">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,10 +1131,10 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C52" s="2">
-        <v>25</v>
+        <v>778</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1148,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C53" s="2">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C55" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,195 +1187,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C56" s="2">
-        <v>2</v>
+        <v>1649</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C57" s="2">
-        <v>56</v>
-      </c>
-      <c r="D57" s="2" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="2">
-        <v>45639</v>
-      </c>
-      <c r="C58" s="2">
-        <v>105</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C59" s="2">
-        <v>5</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C61" s="2">
-        <v>99</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C62" s="2">
-        <v>100</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="2">
-        <v>45635</v>
-      </c>
-      <c r="C63" s="2">
-        <v>2</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="2">
-        <v>45636</v>
-      </c>
-      <c r="C64" s="2">
-        <v>135</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="2">
-        <v>45637</v>
-      </c>
-      <c r="C65" s="2">
-        <v>514</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C66" s="2">
-        <v>2</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C67" s="2">
-        <v>1</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45639</v>
-      </c>
-      <c r="C68" s="2">
-        <v>265</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C69" s="2">
-        <v>1413</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -437,7 +434,7 @@
         <v>45636</v>
       </c>
       <c r="C2" s="2">
-        <v>51</v>
+        <v>642</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C3" s="2">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C4" s="2">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -479,10 +476,10 @@
         <v>45639</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>807</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -493,7 +490,7 @@
         <v>45640</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -504,10 +501,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C7" s="2">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -521,10 +518,10 @@
         <v>45636</v>
       </c>
       <c r="C8" s="2">
-        <v>397</v>
+        <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -535,10 +532,10 @@
         <v>45637</v>
       </c>
       <c r="C9" s="2">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -549,10 +546,10 @@
         <v>45637</v>
       </c>
       <c r="C10" s="2">
-        <v>4</v>
+        <v>535</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +557,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +571,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C12" s="2">
-        <v>573</v>
+        <v>829</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,13 +585,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C13" s="2">
-        <v>570</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,10 +599,10 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C14" s="2">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>6</v>
@@ -616,13 +613,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C15" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C16" s="2">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C17" s="2">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +655,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,13 +669,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C20" s="2">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +697,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45638</v>
+        <v>45636</v>
       </c>
       <c r="C21" s="2">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C22" s="2">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45640</v>
+        <v>45637</v>
       </c>
       <c r="C23" s="2">
+        <v>778</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45641</v>
+        <v>45639</v>
       </c>
       <c r="C24" s="2">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,10 +753,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C25" s="2">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -770,13 +767,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C26" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +781,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45635</v>
+        <v>45640</v>
       </c>
       <c r="C27" s="2">
-        <v>1</v>
+        <v>1649</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,13 +795,13 @@
         <v>4</v>
       </c>
       <c r="B28" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C28" s="2">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,13 +809,13 @@
         <v>4</v>
       </c>
       <c r="B29" s="2">
-        <v>45638</v>
+        <v>45636</v>
       </c>
       <c r="C29" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +823,13 @@
         <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>45638</v>
+        <v>45637</v>
       </c>
       <c r="C30" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +837,13 @@
         <v>4</v>
       </c>
       <c r="B31" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C32" s="2">
-        <v>63</v>
+        <v>514</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -871,10 +868,10 @@
         <v>45640</v>
       </c>
       <c r="C33" s="2">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C34" s="2">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -899,10 +896,10 @@
         <v>45641</v>
       </c>
       <c r="C35" s="2">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -913,10 +910,10 @@
         <v>45641</v>
       </c>
       <c r="C36" s="2">
-        <v>6</v>
+        <v>802</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C37" s="2">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -941,10 +938,10 @@
         <v>45635</v>
       </c>
       <c r="C38" s="2">
-        <v>2</v>
+        <v>735</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -955,10 +952,10 @@
         <v>45636</v>
       </c>
       <c r="C39" s="2">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C40" s="2">
-        <v>514</v>
+        <v>714</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,10 +977,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C41" s="2">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>6</v>
@@ -994,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="C43" s="2">
-        <v>265</v>
+        <v>4</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1019,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C44" s="2">
-        <v>1413</v>
+        <v>65</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>6</v>
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C45" s="2">
-        <v>135</v>
+        <v>55</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1053,10 +1050,10 @@
         <v>45639</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45639</v>
+        <v>45641</v>
       </c>
       <c r="C48" s="2">
-        <v>32</v>
+        <v>1165</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C49" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C50" s="2">
-        <v>1125</v>
+        <v>338</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C51" s="2">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C52" s="2">
-        <v>10</v>
+        <v>816</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C53" s="2">
-        <v>457</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C54" s="2">
-        <v>193</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,13 +1173,13 @@
         <v>4</v>
       </c>
       <c r="B55" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C55" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1190,195 +1187,13 @@
         <v>4</v>
       </c>
       <c r="B56" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C57" s="2">
-        <v>7</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C58" s="2">
-        <v>1</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C59" s="2">
-        <v>403</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C61" s="2">
-        <v>88</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="2">
-        <v>45635</v>
-      </c>
-      <c r="C62" s="2">
-        <v>84</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="2">
-        <v>45635</v>
-      </c>
-      <c r="C63" s="2">
-        <v>2</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="2">
-        <v>45636</v>
-      </c>
-      <c r="C64" s="2">
-        <v>3</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="2">
-        <v>45637</v>
-      </c>
-      <c r="C65" s="2">
-        <v>36</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C66" s="2">
-        <v>102</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C67" s="2">
-        <v>5</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C68" s="2">
-        <v>129</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="2">
-        <v>45641</v>
-      </c>
-      <c r="C69" s="2">
-        <v>137</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
   <si>
     <t>Resort</t>
   </si>
@@ -28,19 +28,22 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Snowbowl</t>
+    <t>Purgatory</t>
   </si>
   <si>
-    <t>Snowbowl Tickets</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
-    <t>Snowbowl Comp Tickets</t>
+    <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Snowbowl Passes</t>
+    <t>Purgatory Coaster</t>
   </si>
   <si>
-    <t>Snowbowl Uplift Tickets</t>
+    <t>Purgatory Tickets</t>
+  </si>
+  <si>
+    <t>Purgatory Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -403,13 +406,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -431,10 +434,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C2" s="2">
-        <v>642</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -445,10 +448,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45637</v>
+        <v>45636</v>
       </c>
       <c r="C3" s="2">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -459,13 +462,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,13 +476,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C5" s="2">
-        <v>807</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C6" s="2">
-        <v>192</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -501,13 +504,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45636</v>
+        <v>45638</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,13 +518,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,13 +532,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45637</v>
+        <v>45640</v>
       </c>
       <c r="C9" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +546,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45637</v>
+        <v>45641</v>
       </c>
       <c r="C10" s="2">
-        <v>535</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,10 +560,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
@@ -571,13 +574,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C12" s="2">
-        <v>829</v>
+        <v>100</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,13 +588,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>397</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,13 +602,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C14" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,13 +616,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="2">
-        <v>45635</v>
+        <v>45637</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +630,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45636</v>
+        <v>45638</v>
       </c>
       <c r="C16" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C17" s="2">
-        <v>64</v>
+        <v>573</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -655,10 +658,10 @@
         <v>4</v>
       </c>
       <c r="B18" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C18" s="2">
-        <v>29</v>
+        <v>570</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -669,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C19" s="2">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,10 +689,10 @@
         <v>45641</v>
       </c>
       <c r="C20" s="2">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C21" s="2">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -725,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C23" s="2">
-        <v>778</v>
+        <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,10 +745,10 @@
         <v>45639</v>
       </c>
       <c r="C24" s="2">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -759,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,13 +770,13 @@
         <v>4</v>
       </c>
       <c r="B26" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C26" s="2">
-        <v>1</v>
+        <v>1125</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -781,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45640</v>
+        <v>45635</v>
       </c>
       <c r="C27" s="2">
-        <v>1649</v>
+        <v>84</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -798,10 +801,10 @@
         <v>45635</v>
       </c>
       <c r="C28" s="2">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -812,10 +815,10 @@
         <v>45636</v>
       </c>
       <c r="C29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,10 +829,10 @@
         <v>45637</v>
       </c>
       <c r="C30" s="2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,10 +843,10 @@
         <v>45638</v>
       </c>
       <c r="C31" s="2">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C32" s="2">
-        <v>514</v>
+        <v>5</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,10 +871,10 @@
         <v>45640</v>
       </c>
       <c r="C33" s="2">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -879,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C34" s="2">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,13 +896,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C35" s="2">
-        <v>74</v>
+        <v>360</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -907,13 +910,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C36" s="2">
-        <v>802</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,13 +924,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C37" s="2">
-        <v>504</v>
+        <v>457</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -935,13 +938,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C38" s="2">
-        <v>735</v>
+        <v>193</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -949,10 +952,10 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45636</v>
+        <v>45638</v>
       </c>
       <c r="C39" s="2">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>6</v>
@@ -963,13 +966,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C40" s="2">
-        <v>714</v>
+        <v>1</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -977,10 +980,10 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C41" s="2">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>6</v>
@@ -994,10 +997,10 @@
         <v>45641</v>
       </c>
       <c r="C42" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,13 +1008,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45635</v>
+        <v>45641</v>
       </c>
       <c r="C43" s="2">
-        <v>4</v>
+        <v>403</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1019,10 +1022,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45635</v>
+        <v>45641</v>
       </c>
       <c r="C44" s="2">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>6</v>
@@ -1033,10 +1036,10 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45638</v>
+        <v>45641</v>
       </c>
       <c r="C45" s="2">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>6</v>
@@ -1047,13 +1050,13 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="C46" s="2">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45640</v>
+        <v>45636</v>
       </c>
       <c r="C47" s="2">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,13 +1078,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C48" s="2">
-        <v>1165</v>
+        <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1089,13 +1092,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C49" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1103,13 +1106,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45636</v>
+        <v>45639</v>
       </c>
       <c r="C50" s="2">
-        <v>338</v>
+        <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,13 +1120,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C51" s="2">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1131,13 +1134,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C52" s="2">
-        <v>816</v>
+        <v>145</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1145,13 +1148,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,13 +1162,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C54" s="2">
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1176,10 +1179,10 @@
         <v>45641</v>
       </c>
       <c r="C55" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,6 +1196,188 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="2">
+        <v>45635</v>
+      </c>
+      <c r="C57" s="2">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B58" s="2">
+        <v>45636</v>
+      </c>
+      <c r="C58" s="2">
+        <v>135</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B59" s="2">
+        <v>45637</v>
+      </c>
+      <c r="C59" s="2">
+        <v>514</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="2">
+        <v>45638</v>
+      </c>
+      <c r="C60" s="2">
+        <v>2</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="2">
+        <v>45638</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B62" s="2">
+        <v>45639</v>
+      </c>
+      <c r="C62" s="2">
+        <v>265</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B63" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1413</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B64" s="2">
+        <v>45636</v>
+      </c>
+      <c r="C64" s="2">
+        <v>51</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B65" s="2">
+        <v>45636</v>
+      </c>
+      <c r="C65" s="2">
+        <v>6</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B66" s="2">
+        <v>45637</v>
+      </c>
+      <c r="C66" s="2">
+        <v>133</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B67" s="2">
+        <v>45639</v>
+      </c>
+      <c r="C67" s="2">
+        <v>2</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B68" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B69" s="2">
+        <v>45640</v>
+      </c>
+      <c r="C69" s="2">
+        <v>88</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/reports/Week Total (Prior Year)_Visits.xlsx
+++ b/reports/Week Total (Prior Year)_Visits.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="9">
   <si>
     <t>Resort</t>
   </si>
@@ -28,22 +28,19 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory</t>
+    <t>Snowbowl</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Snowbowl Tickets</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Snowbowl Comp Tickets</t>
   </si>
   <si>
-    <t>Purgatory Coaster</t>
+    <t>Snowbowl Passes</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Uplift Tickets</t>
+    <t>Snowbowl Uplift Tickets</t>
   </si>
 </sst>
 </file>
@@ -406,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -434,10 +431,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C2" s="2">
-        <v>25</v>
+        <v>642</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,10 +445,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>45636</v>
+        <v>45637</v>
       </c>
       <c r="C3" s="2">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,13 +459,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +473,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>45637</v>
+        <v>45639</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>807</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,10 +487,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>192</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -504,13 +501,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C7" s="2">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -518,10 +515,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>45639</v>
+        <v>45635</v>
       </c>
       <c r="C8" s="2">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -532,10 +529,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C9" s="2">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>6</v>
@@ -546,13 +543,13 @@
         <v>4</v>
       </c>
       <c r="B10" s="2">
-        <v>45641</v>
+        <v>45639</v>
       </c>
       <c r="C10" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,10 +557,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C11" s="2">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>7</v>
@@ -577,7 +574,7 @@
         <v>45641</v>
       </c>
       <c r="C12" s="2">
-        <v>100</v>
+        <v>1165</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -591,10 +588,10 @@
         <v>45636</v>
       </c>
       <c r="C13" s="2">
-        <v>397</v>
+        <v>39</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -605,10 +602,10 @@
         <v>45637</v>
       </c>
       <c r="C14" s="2">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -619,10 +616,10 @@
         <v>45637</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>778</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -630,13 +627,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +641,13 @@
         <v>4</v>
       </c>
       <c r="B17" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C17" s="2">
-        <v>573</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -661,10 +658,10 @@
         <v>45640</v>
       </c>
       <c r="C18" s="2">
-        <v>570</v>
+        <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -675,10 +672,10 @@
         <v>45640</v>
       </c>
       <c r="C19" s="2">
-        <v>48</v>
+        <v>1649</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -686,13 +683,13 @@
         <v>4</v>
       </c>
       <c r="B20" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C20" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,10 +697,10 @@
         <v>4</v>
       </c>
       <c r="B21" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C21" s="2">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -714,13 +711,13 @@
         <v>4</v>
       </c>
       <c r="B22" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +725,13 @@
         <v>4</v>
       </c>
       <c r="B23" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C23" s="2">
-        <v>1</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +739,13 @@
         <v>4</v>
       </c>
       <c r="B24" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C24" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -759,10 +756,10 @@
         <v>45640</v>
       </c>
       <c r="C25" s="2">
-        <v>1</v>
+        <v>829</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -773,10 +770,10 @@
         <v>45641</v>
       </c>
       <c r="C26" s="2">
-        <v>1125</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="B27" s="2">
-        <v>45635</v>
+        <v>45641</v>
       </c>
       <c r="C27" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>6</v>
@@ -804,7 +801,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -815,10 +812,10 @@
         <v>45636</v>
       </c>
       <c r="C29" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -829,10 +826,10 @@
         <v>45637</v>
       </c>
       <c r="C30" s="2">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -843,10 +840,10 @@
         <v>45638</v>
       </c>
       <c r="C31" s="2">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>45640</v>
+        <v>45639</v>
       </c>
       <c r="C32" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -868,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="B33" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C33" s="2">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +879,13 @@
         <v>4</v>
       </c>
       <c r="B34" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C34" s="2">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -896,13 +893,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="2">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="C35" s="2">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -910,13 +907,13 @@
         <v>4</v>
       </c>
       <c r="B36" s="2">
-        <v>45635</v>
+        <v>45638</v>
       </c>
       <c r="C36" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -924,13 +921,13 @@
         <v>4</v>
       </c>
       <c r="B37" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C37" s="2">
-        <v>457</v>
+        <v>816</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -938,13 +935,13 @@
         <v>4</v>
       </c>
       <c r="B38" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C38" s="2">
-        <v>193</v>
+        <v>1</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -952,13 +949,13 @@
         <v>4</v>
       </c>
       <c r="B39" s="2">
-        <v>45638</v>
+        <v>45640</v>
       </c>
       <c r="C39" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +963,13 @@
         <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +977,13 @@
         <v>4</v>
       </c>
       <c r="B41" s="2">
-        <v>45640</v>
+        <v>45641</v>
       </c>
       <c r="C41" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +991,13 @@
         <v>4</v>
       </c>
       <c r="B42" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1005,13 @@
         <v>4</v>
       </c>
       <c r="B43" s="2">
-        <v>45641</v>
+        <v>45635</v>
       </c>
       <c r="C43" s="2">
-        <v>403</v>
+        <v>735</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,10 +1019,10 @@
         <v>4</v>
       </c>
       <c r="B44" s="2">
-        <v>45641</v>
+        <v>45636</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>6</v>
@@ -1036,13 +1033,13 @@
         <v>4</v>
       </c>
       <c r="B45" s="2">
-        <v>45641</v>
+        <v>45638</v>
       </c>
       <c r="C45" s="2">
-        <v>88</v>
+        <v>714</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1050,10 +1047,10 @@
         <v>4</v>
       </c>
       <c r="B46" s="2">
-        <v>45635</v>
+        <v>45639</v>
       </c>
       <c r="C46" s="2">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>6</v>
@@ -1064,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B47" s="2">
-        <v>45636</v>
+        <v>45641</v>
       </c>
       <c r="C47" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1075,13 @@
         <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>45638</v>
+        <v>45635</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1089,13 @@
         <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>45638</v>
+        <v>45636</v>
       </c>
       <c r="C49" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>45639</v>
+        <v>45637</v>
       </c>
       <c r="C50" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1120,13 +1117,13 @@
         <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C51" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1134,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C52" s="2">
-        <v>145</v>
+        <v>514</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1148,13 +1145,13 @@
         <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C53" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1159,13 @@
         <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C54" s="2">
-        <v>2</v>
+        <v>166</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1179,10 +1176,10 @@
         <v>45641</v>
       </c>
       <c r="C55" s="2">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1193,191 +1190,9 @@
         <v>45641</v>
       </c>
       <c r="C56" s="2">
-        <v>1</v>
+        <v>802</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="2">
-        <v>45635</v>
-      </c>
-      <c r="C57" s="2">
-        <v>2</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B58" s="2">
-        <v>45636</v>
-      </c>
-      <c r="C58" s="2">
-        <v>135</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="2">
-        <v>45637</v>
-      </c>
-      <c r="C59" s="2">
-        <v>514</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B60" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C60" s="2">
-        <v>2</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="2">
-        <v>45638</v>
-      </c>
-      <c r="C61" s="2">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B62" s="2">
-        <v>45639</v>
-      </c>
-      <c r="C62" s="2">
-        <v>265</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B63" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C63" s="2">
-        <v>1413</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="2">
-        <v>45636</v>
-      </c>
-      <c r="C64" s="2">
-        <v>51</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B65" s="2">
-        <v>45636</v>
-      </c>
-      <c r="C65" s="2">
-        <v>6</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B66" s="2">
-        <v>45637</v>
-      </c>
-      <c r="C66" s="2">
-        <v>133</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B67" s="2">
-        <v>45639</v>
-      </c>
-      <c r="C67" s="2">
-        <v>2</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B68" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C68" s="2">
-        <v>1</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B69" s="2">
-        <v>45640</v>
-      </c>
-      <c r="C69" s="2">
-        <v>88</v>
-      </c>
-      <c r="D69" s="2" t="s">
         <v>7</v>
       </c>
     </row>
